--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129589931</v>
       </c>
       <c r="B3" t="n">
-        <v>96052</v>
+        <v>96081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129589932</v>
       </c>
       <c r="B4" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129589930</v>
       </c>
       <c r="B5" t="n">
-        <v>95953</v>
+        <v>95982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129589929</v>
       </c>
       <c r="B6" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129589810</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129589931</v>
       </c>
       <c r="B3" t="n">
-        <v>96081</v>
+        <v>96093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129589932</v>
       </c>
       <c r="B4" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129589930</v>
       </c>
       <c r="B5" t="n">
-        <v>95982</v>
+        <v>95994</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129589929</v>
       </c>
       <c r="B6" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129589810</v>
       </c>
       <c r="B7" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129589931</v>
       </c>
       <c r="B3" t="n">
-        <v>96093</v>
+        <v>96094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129589932</v>
       </c>
       <c r="B4" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129589930</v>
       </c>
       <c r="B5" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129589929</v>
       </c>
       <c r="B6" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129589810</v>
       </c>
       <c r="B7" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129589931</v>
       </c>
       <c r="B3" t="n">
-        <v>96094</v>
+        <v>96099</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129589932</v>
       </c>
       <c r="B4" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129589930</v>
       </c>
       <c r="B5" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129589929</v>
       </c>
       <c r="B6" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129589810</v>
       </c>
       <c r="B7" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129589931</v>
       </c>
       <c r="B3" t="n">
-        <v>96099</v>
+        <v>96103</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129589932</v>
       </c>
       <c r="B4" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129589930</v>
       </c>
       <c r="B5" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129589929</v>
       </c>
       <c r="B6" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129589810</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129589931</v>
       </c>
       <c r="B3" t="n">
-        <v>96103</v>
+        <v>96105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129589932</v>
       </c>
       <c r="B4" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129589930</v>
       </c>
       <c r="B5" t="n">
-        <v>96004</v>
+        <v>96006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129589929</v>
       </c>
       <c r="B6" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129589810</v>
       </c>
       <c r="B7" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129589931</v>
       </c>
       <c r="B3" t="n">
-        <v>96105</v>
+        <v>96115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129589932</v>
       </c>
       <c r="B4" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129589930</v>
       </c>
       <c r="B5" t="n">
-        <v>96006</v>
+        <v>96016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129589929</v>
       </c>
       <c r="B6" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129589931</v>
       </c>
       <c r="B3" t="n">
-        <v>96115</v>
+        <v>96119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129589932</v>
       </c>
       <c r="B4" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129589930</v>
       </c>
       <c r="B5" t="n">
-        <v>96016</v>
+        <v>96020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129589929</v>
       </c>
       <c r="B6" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129589810</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129589927</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129589931</v>
       </c>
       <c r="B3" t="n">
-        <v>96119</v>
+        <v>96122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129589932</v>
       </c>
       <c r="B4" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129589930</v>
       </c>
       <c r="B5" t="n">
-        <v>96020</v>
+        <v>96023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129589929</v>
       </c>
       <c r="B6" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129589810</v>
       </c>
       <c r="B7" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -1269,7 +1269,7 @@
         <v>131024917</v>
       </c>
       <c r="B8" t="n">
-        <v>96359</v>
+        <v>96361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>131024929</v>
       </c>
       <c r="B9" t="n">
-        <v>91340</v>
+        <v>91342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>131024927</v>
       </c>
       <c r="B10" t="n">
-        <v>93130</v>
+        <v>93132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>131024928</v>
       </c>
       <c r="B11" t="n">
-        <v>93130</v>
+        <v>93132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -1269,7 +1269,7 @@
         <v>131024917</v>
       </c>
       <c r="B8" t="n">
-        <v>96361</v>
+        <v>96362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>131024929</v>
       </c>
       <c r="B9" t="n">
-        <v>91342</v>
+        <v>91343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>131024927</v>
       </c>
       <c r="B10" t="n">
-        <v>93132</v>
+        <v>93133</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>131024928</v>
       </c>
       <c r="B11" t="n">
-        <v>93132</v>
+        <v>93133</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129589927</v>
+        <v>129589810</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630322</v>
+        <v>630369</v>
       </c>
       <c r="R2" t="n">
-        <v>6724566</v>
+        <v>6724601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>gnag</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Ellinor Delin, Jenny Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -784,7 +775,7 @@
         <v>129589931</v>
       </c>
       <c r="B3" t="n">
-        <v>96122</v>
+        <v>96437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129589932</v>
+        <v>131024934</v>
       </c>
       <c r="B4" t="n">
-        <v>100986</v>
+        <v>96231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630348</v>
+        <v>630561</v>
       </c>
       <c r="R4" t="n">
-        <v>6724453</v>
+        <v>6724696</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -943,12 +934,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -959,16 +955,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>stort block</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -978,7 +984,7 @@
         <v>129589930</v>
       </c>
       <c r="B5" t="n">
-        <v>96023</v>
+        <v>96338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129589929</v>
+        <v>131024917</v>
       </c>
       <c r="B6" t="n">
-        <v>100986</v>
+        <v>96458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,37 +1089,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630391</v>
+        <v>630350</v>
       </c>
       <c r="R6" t="n">
-        <v>6724605</v>
+        <v>6724557</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1137,12 +1143,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stora Enso naturvärdesbedömning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1153,64 +1164,74 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>lövträdslåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson, Ellinor Delin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129589810</v>
+        <v>131024929</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
+        <v>91435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5747</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fleräng, Skutskär, Upl</t>
+          <t>Fleräng, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630369</v>
+        <v>630325</v>
       </c>
       <c r="R7" t="n">
-        <v>6724601</v>
+        <v>6724586</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1242,6 +1263,11 @@
           <t>2025-08-15</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ljus fot, blekgula grenar, citrongula toppar, ca 1 dm hög, ingen lukt och smak i fält, men efter torkning påtaglig men svag lukt som drar mot anis, spormått stämmer. Stora Enso naturvärdesbedömning.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1250,26 +1276,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ellinor Delin</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ellinor Delin, Jenny Andersson</t>
+          <t>Jenny Andersson, Ellinor Delin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131024917</v>
+        <v>129589927</v>
       </c>
       <c r="B8" t="n">
-        <v>96362</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,37 +1308,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630350</v>
+        <v>630322</v>
       </c>
       <c r="R8" t="n">
-        <v>6724557</v>
+        <v>6724566</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1331,17 +1366,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1352,74 +1387,68 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>lövträdslåga</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jenny Andersson, Ellinor Delin</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131024929</v>
+        <v>129589942</v>
       </c>
       <c r="B9" t="n">
-        <v>91343</v>
+        <v>8455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5747</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630325</v>
+        <v>630515</v>
       </c>
       <c r="R9" t="n">
-        <v>6724586</v>
+        <v>6724590</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1443,17 +1472,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ljus fot, blekgula grenar, citrongula toppar, ca 1 dm hög, ingen lukt och smak i fält, men efter torkning påtaglig men svag lukt som drar mot anis, spormått stämmer. Stora Enso naturvärdesbedömning.</t>
+          <t>gnag</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1464,65 +1493,64 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jenny Andersson, Ellinor Delin</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131024927</v>
+        <v>129589934</v>
       </c>
       <c r="B10" t="n">
-        <v>93133</v>
+        <v>99096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630354</v>
+        <v>630377</v>
       </c>
       <c r="R10" t="n">
-        <v>6724479</v>
+        <v>6724468</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,17 +1574,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Den variant som drar mot lila i färgerna. Stora Enso naturvärdesbedömning.</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1565,68 +1588,66 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jenny Andersson, Ellinor Delin</t>
+          <t>Ellinor Delin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131024928</v>
+        <v>129589991</v>
       </c>
       <c r="B11" t="n">
-        <v>93133</v>
+        <v>99096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fleräng, Upl</t>
+          <t>Fleräng, Skutskär, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630325</v>
+        <v>630424</v>
       </c>
       <c r="R11" t="n">
-        <v>6724586</v>
+        <v>6724693</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1650,17 +1671,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Stora Enso naturvärdesbedömning.</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1669,27 +1685,904 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>äldre kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129589997</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>630493</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6724708</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131024932</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fleräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>630419</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6724706</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stora Enso naturvärdesbedömning.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Jenny Andersson</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Jenny Andersson, Ellinor Delin</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129589943</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102240</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>630516</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6724588</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129589989</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>630408</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6724687</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129589994</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>630512</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6724685</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129589929</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>630391</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6724605</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129589932</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>630348</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6724453</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129589992</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>630439</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6724710</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129589809</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93225</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fleräng, Skutskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>630397</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6724623</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ellinor Delin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ellinor Delin, Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51149-2025 artfynd.xlsx
+++ b/artfynd/A 51149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589810</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589931</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024934</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589930</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024917</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024929</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589927</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589942</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589934</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589991</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1797,6 +1852,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589997</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024932</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589943</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2098,6 +2168,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589989</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2195,6 +2270,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589994</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589929</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589932</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2486,6 +2576,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589992</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2583,8 +2678,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129589809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>